--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053859</t>
+          <t xml:space="preserve">311053869</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">factum2 Horsens</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084316</t>
+          <t xml:space="preserve">311084392</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">

--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -8479,12 +8479,12 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -5839,12 +5839,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053869</t>
+          <t xml:space="preserve">311053859</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Horsens</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084392</t>
+          <t xml:space="preserve">311084316</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
